--- a/product-definitions/spreadsheet/_instrument_vocabs.xlsx
+++ b/product-definitions/spreadsheet/_instrument_vocabs.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="756">
   <si>
     <t>Instrument</t>
   </si>
@@ -2317,6 +2317,24 @@
   </si>
   <si>
     <t>NCAS Sonic Anemometer unit 6</t>
+  </si>
+  <si>
+    <t>Metek</t>
+  </si>
+  <si>
+    <t>USA-1</t>
+  </si>
+  <si>
+    <t>200607005/01</t>
+  </si>
+  <si>
+    <t>cfarr-sonic-anemometer</t>
+  </si>
+  <si>
+    <t>ncas-sonic-5</t>
+  </si>
+  <si>
+    <t>NCAS Sonic Anemometer unit 5</t>
   </si>
 </sst>
 </file>
@@ -37138,6 +37156,47 @@
       <c r="M157" s="38"/>
       <c r="N157" s="38"/>
     </row>
+    <row r="158">
+      <c r="A158" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B158" s="37" t="s">
+        <v>750</v>
+      </c>
+      <c r="C158" s="37" t="s">
+        <v>751</v>
+      </c>
+      <c r="D158" s="37" t="s">
+        <v>752</v>
+      </c>
+      <c r="E158" s="37" t="s">
+        <v>753</v>
+      </c>
+      <c r="F158" s="37" t="s">
+        <v>754</v>
+      </c>
+      <c r="G158" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="H158" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="I158" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="J158" s="37" t="s">
+        <v>573</v>
+      </c>
+      <c r="K158" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="L158" s="37" t="s">
+        <v>755</v>
+      </c>
+      <c r="M158" s="37" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
